--- a/sample_assets/data_auto.xlsx
+++ b/sample_assets/data_auto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,16 @@
           <t>Footer</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Voiceover</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Screen_Text</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,6 +459,12 @@
           <t>Offer ends June 30</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Summer mega sale is here. Up to fifty percent off everything. Offer ends June thirtieth.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -458,6 +474,8 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -475,6 +493,16 @@
           <t>www.example.com</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New arrivals just landed, with fresh styles every week.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>New in. Fresh styles every week.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -488,6 +516,8 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -503,6 +533,12 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Follow us for daily dance tutorials and behind the scenes fun</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No narration here. Just timed captions. Read them at your own pace.</t>
         </is>
       </c>
     </row>
